--- a/docs/MeerKit_테이블명세서.xlsx
+++ b/docs/MeerKit_테이블명세서.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="관계" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컬럼 명세'!$A$1:$L$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컬럼 명세'!$A$1:$L$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,6 +513,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -533,7 +534,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>5aeec7c9a772</t>
+          <t>d129bc5cc95b</t>
         </is>
       </c>
     </row>
@@ -545,7 +546,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>main bae1b41 (PR #13 병합)</t>
+          <t>main fe80117 (PR #29 병합)</t>
         </is>
       </c>
     </row>
@@ -557,7 +558,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-25 (2026-10-27 users.avatar_key 추가)</t>
         </is>
       </c>
     </row>
@@ -585,6 +586,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -639,7 +641,7 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -810,7 +812,7 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1603,12 +1605,12 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>email_verified_at</t>
+          <t>avatar_key</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -1616,14 +1618,14 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="11" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
-      <c r="K18" s="11" t="inlineStr"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="11" t="n"/>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>이메일 인증 완료 시각 (NULL이면 미인증)</t>
+          <t>프로필 이미지 파일의 저장소 key (avatars/&lt;무작위&gt;.webp). 교체·삭제·파기 때 이전 파일을 지우는 데 씀. 파일은 Supabase Storage 버킷 meerkit-public에 있음</t>
         </is>
       </c>
     </row>
@@ -1643,31 +1645,27 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>failed_login_count</t>
+          <t>email_verified_at</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr"/>
       <c r="H19" s="10" t="inlineStr"/>
       <c r="I19" s="11" t="inlineStr"/>
       <c r="J19" s="10" t="inlineStr"/>
       <c r="K19" s="11" t="inlineStr"/>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>연속 로그인 실패 횟수 (성공·잠금 시 0으로 초기화)</t>
+          <t>이메일 인증 완료 시각 (NULL이면 미인증)</t>
         </is>
       </c>
     </row>
@@ -1687,27 +1685,31 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>locked_until</t>
+          <t>failed_login_count</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H20" s="10" t="inlineStr"/>
       <c r="I20" s="11" t="inlineStr"/>
       <c r="J20" s="10" t="inlineStr"/>
       <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>로그인 잠금 해제 시각 (5회 실패 → 5분)</t>
+          <t>연속 로그인 실패 횟수 (성공·잠금 시 0으로 초기화)</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1729,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>last_login_at</t>
+          <t>locked_until</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -1747,7 +1749,7 @@
       <c r="K21" s="11" t="inlineStr"/>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>마지막 로그인 시각</t>
+          <t>로그인 잠금 해제 시각 (5회 실패 → 5분)</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1769,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>password_changed_at</t>
+          <t>last_login_at</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -1787,7 +1789,7 @@
       <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>비밀번호 변경 시각. 이전에 발급된 토큰은 거부</t>
+          <t>마지막 로그인 시각</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1809,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>deactivated_at</t>
+          <t>password_changed_at</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -1827,7 +1829,7 @@
       <c r="K23" s="11" t="inlineStr"/>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>탈퇴(또는 관리자 삭제) 시각. 보관 기간 계산 기준</t>
+          <t>비밀번호 변경 시각. 이전에 발급된 토큰은 거부</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1849,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>deactivated_at</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -1867,55 +1869,47 @@
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr">
         <is>
+          <t>탈퇴(또는 관리자 삭제) 시각. 보관 기간 계산 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr"/>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
           <t>개인정보 파기 시각 (탈퇴 후 365일, purge 명령)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>roles</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>자동 증가</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr"/>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>역할 번호 (1 MASTER, 2 OWNER, 3 VIEWER, 4 WRITER)</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1929,12 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -1948,22 +1942,22 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="I26" s="8" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>UNIQUE roles_code_key</t>
-        </is>
-      </c>
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="8" t="inlineStr"/>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>역할 코드. 코드에서 비교하는 값</t>
+          <t>역할 번호 (1 MASTER, 2 OWNER, 3 VIEWER, 4 WRITER)</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1977,12 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>code</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -1999,59 +1993,59 @@
       <c r="G27" s="8" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" s="8" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="8" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>UNIQUE roles_code_key</t>
+        </is>
+      </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
+          <t>역할 코드. 코드에서 비교하는 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>roles</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="8" t="inlineStr"/>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="8" t="inlineStr"/>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
           <t>화면 표시용 설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>user_roles</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>회원-역할 연결</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr"/>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>users.id (ON DELETE CASCADE)</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr"/>
-      <c r="K28" s="11" t="inlineStr"/>
-      <c r="L28" s="11" t="inlineStr">
-        <is>
-          <t>회원 번호</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2065,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -2092,62 +2086,62 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>roles.id (ON DELETE CASCADE)</t>
+          <t>users.id (ON DELETE CASCADE)</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr"/>
       <c r="K29" s="11" t="inlineStr"/>
       <c r="L29" s="11" t="inlineStr">
         <is>
+          <t>회원 번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>user_roles</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>회원-역할 연결</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>role_id</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr"/>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>roles.id (ON DELETE CASCADE)</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr"/>
+      <c r="K30" s="11" t="inlineStr"/>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
           <t>역할 번호</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>terms</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>약관</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>자동 증가</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr"/>
-      <c r="J30" s="6" t="inlineStr"/>
-      <c r="K30" s="8" t="inlineStr"/>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>약관 번호</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2161,12 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -2180,22 +2174,22 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="I31" s="8" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>복합(code, version)</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>UNIQUE terms_code_version_key</t>
-        </is>
-      </c>
+      <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr"/>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t>약관 코드 (terms / privacy / marketing)</t>
+          <t>약관 번호</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2209,12 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>code</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -2243,7 +2237,7 @@
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>약관 버전. 문구가 바뀌면 새 행 추가</t>
+          <t>약관 코드 (terms / privacy / marketing)</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2257,12 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>version</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -2279,11 +2273,19 @@
       <c r="G33" s="8" t="inlineStr"/>
       <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr"/>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>복합(code, version)</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>UNIQUE terms_code_version_key</t>
+        </is>
+      </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>약관 제목</t>
+          <t>약관 버전. 문구가 바뀌면 새 행 추가</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2305,12 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>is_required</t>
+          <t>title</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -2323,7 +2325,7 @@
       <c r="K34" s="8" t="inlineStr"/>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>필수 동의 여부</t>
+          <t>약관 제목</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2345,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>is_required</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -2356,18 +2358,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+      <c r="G35" s="8" t="inlineStr"/>
       <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="6" t="inlineStr"/>
       <c r="K35" s="8" t="inlineStr"/>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>현재 버전 여부 (가입 화면에 보이는 약관)</t>
+          <t>필수 동의 여부</t>
         </is>
       </c>
     </row>
@@ -2387,12 +2385,12 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -2402,7 +2400,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>true</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2411,55 +2409,51 @@
       <c r="K36" s="8" t="inlineStr"/>
       <c r="L36" s="8" t="inlineStr">
         <is>
+          <t>현재 버전 여부 (가입 화면에 보이는 약관)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>terms</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>약관</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
           <t>등록 시각</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>user_term_agreements</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>약관 동의 기록</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>users.id (ON DELETE CASCADE)</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr"/>
-      <c r="K37" s="11" t="inlineStr"/>
-      <c r="L37" s="11" t="inlineStr">
-        <is>
-          <t>회원 번호</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2473,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>term_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -2500,14 +2494,14 @@
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>terms.id</t>
+          <t>users.id (ON DELETE CASCADE)</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr"/>
       <c r="K38" s="11" t="inlineStr"/>
       <c r="L38" s="11" t="inlineStr">
         <is>
-          <t>약관 번호 (버전 포함)</t>
+          <t>회원 번호</t>
         </is>
       </c>
     </row>
@@ -2527,12 +2521,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>agreed_at</t>
+          <t>term_id</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
@@ -2540,66 +2534,66 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr"/>
-      <c r="I39" s="11" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>terms.id</t>
+        </is>
+      </c>
       <c r="J39" s="10" t="inlineStr"/>
       <c r="K39" s="11" t="inlineStr"/>
       <c r="L39" s="11" t="inlineStr">
         <is>
+          <t>약관 번호 (버전 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>user_term_agreements</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>약관 동의 기록</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>agreed_at</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr"/>
+      <c r="I40" s="11" t="inlineStr"/>
+      <c r="J40" s="10" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
+      <c r="L40" s="11" t="inlineStr">
+        <is>
           <t>동의 시각</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>email_verifications</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>이메일 인증번호</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>자동 증가</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr"/>
-      <c r="J40" s="6" t="inlineStr"/>
-      <c r="K40" s="8" t="inlineStr"/>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t>인증 기록 번호 (가입 증표 토큰에 들어감)</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2613,12 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(255)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -2632,18 +2626,22 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="I41" s="8" t="inlineStr"/>
       <c r="J41" s="6" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>ix_email_verifications_email</t>
-        </is>
-      </c>
+      <c r="K41" s="8" t="inlineStr"/>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>인증할 이메일</t>
+          <t>인증 기록 번호 (가입 증표 토큰에 들어감)</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2661,12 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>code_hash</t>
+          <t>email</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -2680,10 +2678,14 @@
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="8" t="inlineStr"/>
       <c r="J42" s="6" t="inlineStr"/>
-      <c r="K42" s="8" t="inlineStr"/>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>ix_email_verifications_email</t>
+        </is>
+      </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>6자리 인증번호의 HMAC-SHA256 해시</t>
+          <t>인증할 이메일</t>
         </is>
       </c>
     </row>
@@ -2703,12 +2705,12 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>expires_at</t>
+          <t>code_hash</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -2723,7 +2725,7 @@
       <c r="K43" s="8" t="inlineStr"/>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>인증번호 만료 시각 (발송 후 10분)</t>
+          <t>6자리 인증번호의 HMAC-SHA256 해시</t>
         </is>
       </c>
     </row>
@@ -2743,12 +2745,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>attempts</t>
+          <t>expires_at</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -2756,18 +2758,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="G44" s="8" t="inlineStr"/>
       <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="8" t="inlineStr"/>
       <c r="J44" s="6" t="inlineStr"/>
       <c r="K44" s="8" t="inlineStr"/>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>틀린 횟수 (5회 이상이면 무효)</t>
+          <t>인증번호 만료 시각 (발송 후 10분)</t>
         </is>
       </c>
     </row>
@@ -2787,27 +2785,31 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>verified_at</t>
+          <t>attempts</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="8" t="inlineStr"/>
       <c r="J45" s="6" t="inlineStr"/>
       <c r="K45" s="8" t="inlineStr"/>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>인증번호 확인 성공 시각</t>
+          <t>틀린 횟수 (5회 이상이면 무효)</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2829,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>used_at</t>
+          <t>verified_at</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -2847,7 +2849,7 @@
       <c r="K46" s="8" t="inlineStr"/>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>가입(또는 이메일 변경)에 사용된 시각 (한 번만)</t>
+          <t>인증번호 확인 성공 시각</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2869,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>used_at</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -2877,73 +2879,65 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr"/>
       <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="8" t="inlineStr"/>
       <c r="J47" s="6" t="inlineStr"/>
-      <c r="K47" s="8" t="inlineStr">
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>가입(또는 이메일 변경)에 사용된 시각 (한 번만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>email_verifications</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>이메일 인증번호</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="8" t="inlineStr"/>
+      <c r="J48" s="6" t="inlineStr"/>
+      <c r="K48" s="8" t="inlineStr">
         <is>
           <t>ix_email_verifications_created_at</t>
         </is>
       </c>
-      <c r="L47" s="8" t="inlineStr">
+      <c r="L48" s="8" t="inlineStr">
         <is>
           <t>발송 시각. 60초 간격·하루 10회 제한 계산, 7일 뒤 삭제</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>password_reset_tokens</t>
-        </is>
-      </c>
-      <c r="C48" s="11" t="inlineStr">
-        <is>
-          <t>비밀번호 재설정 토큰</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>자동 증가</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="inlineStr"/>
-      <c r="J48" s="10" t="inlineStr"/>
-      <c r="K48" s="11" t="inlineStr"/>
-      <c r="L48" s="11" t="inlineStr">
-        <is>
-          <t>토큰 번호</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2957,7 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -2976,22 +2970,22 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G49" s="11" t="inlineStr"/>
-      <c r="H49" s="10" t="inlineStr"/>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>users.id (ON DELETE CASCADE)</t>
-        </is>
-      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr"/>
       <c r="J49" s="10" t="inlineStr"/>
-      <c r="K49" s="11" t="inlineStr">
-        <is>
-          <t>ix_password_reset_tokens_user_id</t>
-        </is>
-      </c>
+      <c r="K49" s="11" t="inlineStr"/>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>회원 번호</t>
+          <t>토큰 번호</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3005,12 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>token_hash</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -3026,20 +3020,20 @@
       </c>
       <c r="G50" s="11" t="inlineStr"/>
       <c r="H50" s="10" t="inlineStr"/>
-      <c r="I50" s="11" t="inlineStr"/>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>users.id (ON DELETE CASCADE)</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr">
         <is>
-          <t>UNIQUE password_reset_tokens_token_hash_key</t>
+          <t>ix_password_reset_tokens_user_id</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>링크 토큰의 HMAC-SHA256 해시 (원문은 메일로만)</t>
+          <t>회원 번호</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3053,12 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>expires_at</t>
+          <t>token_hash</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
@@ -3075,11 +3069,19 @@
       <c r="G51" s="11" t="inlineStr"/>
       <c r="H51" s="10" t="inlineStr"/>
       <c r="I51" s="11" t="inlineStr"/>
-      <c r="J51" s="10" t="inlineStr"/>
-      <c r="K51" s="11" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>UNIQUE password_reset_tokens_token_hash_key</t>
+        </is>
+      </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>만료 시각 (발송 후 30분)</t>
+          <t>링크 토큰의 HMAC-SHA256 해시 (원문은 메일로만)</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3101,7 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>used_at</t>
+          <t>expires_at</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -3109,7 +3111,7 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr"/>
@@ -3119,7 +3121,7 @@
       <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr">
         <is>
-          <t>사용(또는 무효화) 시각</t>
+          <t>만료 시각 (발송 후 30분)</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3141,7 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>used_at</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
@@ -3149,70 +3151,110 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr"/>
       <c r="I53" s="11" t="inlineStr"/>
       <c r="J53" s="10" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr"/>
       <c r="L53" s="11" t="inlineStr">
         <is>
+          <t>사용(또는 무효화) 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>password_reset_tokens</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>비밀번호 재설정 토큰</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr"/>
+      <c r="I54" s="11" t="inlineStr"/>
+      <c r="J54" s="10" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr"/>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
           <t>발송 시각. 발송 횟수 제한 계산</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>alembic_version</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>마이그레이션 버전</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>version_num</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>VARCHAR(32)</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr"/>
-      <c r="J54" s="6" t="inlineStr"/>
-      <c r="K54" s="8" t="inlineStr"/>
-      <c r="L54" s="8" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr"/>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="8" t="inlineStr"/>
+      <c r="L55" s="8" t="inlineStr">
         <is>
           <t>현재 마이그레이션 리비전</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L54"/>
+  <autoFilter ref="A1:L55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/MeerKit_테이블명세서.xlsx
+++ b/docs/MeerKit_테이블명세서.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>d129bc5cc95b</t>
+          <t>bba337f809ab</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>main fe80117 (PR #29 병합)</t>
+          <t>feat/kit-codes (공통코드 추가)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25 (2026-10-27 users.avatar_key 추가)</t>
+          <t>2026-10-25 (2026-10-27 users.avatar_key 추가, 2026-10-29 common_code_groups·common_codes 추가). 소셜 로그인(social_accounts, users.has_password)은 아직 미반영</t>
         </is>
       </c>
     </row>
@@ -788,31 +788,77 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
+          <t>common_code_groups</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>공통코드 묶음</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>킷·서브 서비스 공용 분류값 묶음 (예: MMS_REQ_KIND). owner(MEERKIT/MMS)로 구분, group_code는 owner_ 로 시작</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>common_codes</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>공통코드 값</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>묶음 안의 값 (예: FUNCTIONAL=기능). 끄면 새로 고를 수 없음, 삭제 대신 끄기</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
           <t>alembic_version</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>마이그레이션 버전</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Alembic이 관리. 직접 수정하지 않음</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E21" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="D20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="E20" s="9" t="n">
-        <v>54</v>
+      <c r="E22" s="9" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3210,44 +3256,652 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n">
+      <c r="A55" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>common_code_groups</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 묶음</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>group_code</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="11" t="n"/>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>묶음 코드 (예: MMS_REQ_KIND). 대문자·숫자·_, owner + "_" 로 시작 (CHECK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>common_code_groups</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 묶음</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="10" t="n"/>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>ix_common_code_groups_owner</t>
+        </is>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
+          <t>누구의 코드인지: MEERKIT(킷) / MMS(매무새). 대문자·숫자 (CHECK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>common_code_groups</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 묶음</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="11" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="11" t="n"/>
+      <c r="L57" s="11" t="inlineStr">
+        <is>
+          <t>묶음 이름 (요구사항 구분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>common_code_groups</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 묶음</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="11" t="n"/>
+      <c r="L58" s="11" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>common_code_groups</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 묶음</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="10" t="n"/>
+      <c r="K59" s="11" t="n"/>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>묶음 사용 여부. false면 조회 API에서 안 보임</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>common_code_groups</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 묶음</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="11" t="n"/>
+      <c r="L60" s="11" t="inlineStr">
+        <is>
+          <t>만든 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>common_code_groups</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 묶음</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="10" t="n"/>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>마지막 수정 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>common_codes</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 값</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>group_code</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G62" s="11" t="n"/>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>common_code_groups.group_code (ON DELETE CASCADE)</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>묶음 코드</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>common_codes</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 값</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="n"/>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>DB에 저장하는 값 (예: FUNCTIONAL). 대문자로 시작, 대문자·숫자·_ (CHECK). 바꾸지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>common_codes</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 값</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="11" t="n"/>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>화면 이름 (기능). MASTER가 바꿀 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>common_codes</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 값</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="10" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>목록 순서 (작을수록 위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>common_codes</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 값</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="11" t="n"/>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>끄면 새로 고를 수 없음 (require_code 거절). 이미 저장된 데이터는 그대로</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>common_codes</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 값</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>만든 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>common_codes</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>공통코드 값</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="10" t="n"/>
+      <c r="K68" s="11" t="n"/>
+      <c r="L68" s="11" t="inlineStr">
+        <is>
+          <t>마지막 수정 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>alembic_version</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>마이그레이션 버전</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>version_num</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>VARCHAR(32)</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G55" s="8" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr"/>
-      <c r="J55" s="6" t="inlineStr"/>
-      <c r="K55" s="8" t="inlineStr"/>
-      <c r="L55" s="8" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr"/>
+      <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="8" t="inlineStr"/>
+      <c r="L69" s="8" t="inlineStr">
         <is>
           <t>현재 마이그레이션 리비전</t>
         </is>
@@ -3265,7 +3919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3500,8 +4154,41 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>common_codes</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>group_code</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>common_code_groups.group_code</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>묶음 삭제 시 값도 삭제 (서브 서비스를 뺄 때 owner 묶음만 지우면 됨)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>참고: 회원은 실제로 지우지 않고(탈퇴는 deactivated_at, 365일 뒤 개인정보만 파기), 행을 남겨 다른 데이터의 참조가 깨지지 않게 합니다.</t>
         </is>

--- a/docs/MeerKit_테이블명세서.xlsx
+++ b/docs/MeerKit_테이블명세서.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="관계" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컬럼 명세'!$A$1:$L$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'컬럼 명세'!$A$1:$L$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -534,7 +533,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>bba337f809ab</t>
+          <t>24601a874fac</t>
         </is>
       </c>
     </row>
@@ -546,7 +545,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>feat/kit-codes (공통코드 추가)</t>
+          <t>feat/maemusae-m1 (매무새 프로젝트·멤버 추가)</t>
         </is>
       </c>
     </row>
@@ -558,7 +557,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25 (2026-10-27 users.avatar_key 추가, 2026-10-29 common_code_groups·common_codes 추가). 소셜 로그인(social_accounts, users.has_password)은 아직 미반영</t>
+          <t>2026-10-25 (2026-10-27 users.avatar_key 추가, 2026-10-29 common_code_groups·common_codes, mms_projects·mms_project_members 추가). 소셜 로그인(social_accounts, users.has_password)은 아직 미반영</t>
         </is>
       </c>
     </row>
@@ -586,7 +585,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -834,31 +832,77 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
+          <t>mms_projects</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>서브 서비스 매무새의 프로젝트 (이름·기간). 삭제는 deleted_at 표시 후 보관 기간 뒤 정리</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 멤버</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>프로젝트와 회원의 다대다 연결 + 프로젝트 안 역할(ADMIN 관리자 / MEMBER 일반). 킷 역할과 별개</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
           <t>alembic_version</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>마이그레이션 버전</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>Alembic이 관리. 직접 수정하지 않음</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="D22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>68</v>
+      <c r="E24" s="9" t="n">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3864,51 +3908,711 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n">
+      <c r="A69" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>프로젝트 번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="11" t="n"/>
+      <c r="L70" s="11" t="inlineStr">
+        <is>
+          <t>프로젝트명 (목록 검색 대상, 앞뒤 공백 지움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="10" t="n"/>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>시작일</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G72" s="11" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="11" t="n"/>
+      <c r="L72" s="11" t="inlineStr">
+        <is>
+          <t>종료일. CHECK end_date &gt;= start_date (ck_mms_projects_period)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="n"/>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>만든 사람 (첫 관리자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G74" s="11" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="10" t="n"/>
+      <c r="K74" s="11" t="n"/>
+      <c r="L74" s="11" t="inlineStr">
+        <is>
+          <t>삭제 표시 시각. 값이 있으면 모든 API에서 없는 것으로 봄 (실제 삭제는 보관 기간 뒤 정리 명령)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="10" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
+          <t>만든 시각 (목록 정렬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="11" t="n"/>
+      <c r="L76" s="11" t="inlineStr">
+        <is>
+          <t>마지막 수정 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 멤버</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>멤버 번호 (역할 변경·내보내기 API 경로에 씀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 멤버</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G78" s="11" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects.id</t>
+        </is>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>Y (project_id, user_id)</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="n"/>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>프로젝트. 프로젝트 행이 지워지면 같이 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 멤버</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>Y (project_id, user_id)</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>ix_mms_project_members_user_id</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>회원 (내 프로젝트 목록 조회)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 멤버</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G80" s="11" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="11" t="n"/>
+      <c r="L80" s="11" t="inlineStr">
+        <is>
+          <t>ADMIN(관리자) / MEMBER(일반). CHECK. 프로젝트에 관리자가 1명 이상 남아야 함 (서비스에서 검사)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 멤버</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>joined_at</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="11" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="11" t="n"/>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>참여 시각 (만든 때 또는 초대 수락 때)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 멤버</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="n"/>
+      <c r="I82" s="11" t="n"/>
+      <c r="J82" s="10" t="n"/>
+      <c r="K82" s="11" t="n"/>
+      <c r="L82" s="11" t="inlineStr">
+        <is>
+          <t>만든 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 멤버</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="11" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="11" t="n"/>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>마지막 수정 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>alembic_version</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>마이그레이션 버전</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>version_num</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>VARCHAR(32)</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr"/>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr"/>
-      <c r="J69" s="6" t="inlineStr"/>
-      <c r="K69" s="8" t="inlineStr"/>
-      <c r="L69" s="8" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr"/>
+      <c r="J84" s="6" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr"/>
+      <c r="L84" s="8" t="inlineStr">
         <is>
           <t>현재 마이그레이션 리비전</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L55"/>
+  <autoFilter ref="A1:L84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3919,7 +4623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4125,70 +4829,166 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>email_verifications</t>
+          <t>mms_projects</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>users.id</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N:1</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>RESTRICT</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>가입 전 기록이라 FK 없음 (email로 구분)</t>
+          <t>만든 사람. 회원은 지우지 않고 파기만 하므로 참조가 남음</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>mms_projects.id</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N:1 (projects:users = N:M)</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>프로젝트 행이 지워지면 멤버도 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>RESTRICT</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>회원 (탈퇴해도 행이 남아 참조 유지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>email_verifications</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>(없음)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>가입 전 기록이라 FK 없음 (email로 구분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t>common_codes</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>group_code</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>common_code_groups.group_code</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>N:1</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>CASCADE</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>묶음 삭제 시 값도 삭제 (서브 서비스를 뺄 때 owner 묶음만 지우면 됨)</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>참고: 회원은 실제로 지우지 않고(탈퇴는 deactivated_at, 365일 뒤 개인정보만 파기), 행을 남겨 다른 데이터의 참조가 깨지지 않게 합니다.</t>
         </is>

--- a/docs/MeerKit_테이블명세서.xlsx
+++ b/docs/MeerKit_테이블명세서.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -513,6 +513,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -533,7 +534,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>24601a874fac</t>
+          <t>7b35839667fd</t>
         </is>
       </c>
     </row>
@@ -545,7 +546,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>feat/maemusae-m1 (매무새 프로젝트·멤버 추가)</t>
+          <t>feat/maemusae-invites (매무새 초대 추가)</t>
         </is>
       </c>
     </row>
@@ -557,7 +558,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25 (2026-10-27 users.avatar_key 추가, 2026-10-29 common_code_groups·common_codes, mms_projects·mms_project_members 추가). 소셜 로그인(social_accounts, users.has_password)은 아직 미반영</t>
+          <t>2026-10-25 (2026-10-27 users.avatar_key 추가, 2026-10-29 common_code_groups·common_codes, mms_projects·mms_project_members, mms_project_invitations·mms_project_members.invitation_id 추가). 소셜 로그인(social_accounts, users.has_password)은 아직 미반영</t>
         </is>
       </c>
     </row>
@@ -585,6 +586,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -869,7 +871,7 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -878,31 +880,54 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>프로젝트 관리자가 이메일로 보낸 초대. 토큰은 해시만, 7일·1회, 다시 초대하면 이전 초대 무효. 수락하면 멤버 행 추가</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
           <t>alembic_version</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>마이그레이션 버전</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Alembic이 관리. 직접 수정하지 않음</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E24" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="D24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="E24" s="9" t="n">
-        <v>83</v>
+      <c r="E25" s="9" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -916,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4495,31 +4520,31 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>invitation_id</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G82" s="11" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="n"/>
       <c r="H82" s="10" t="n"/>
-      <c r="I82" s="11" t="n"/>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations.id</t>
+        </is>
+      </c>
       <c r="J82" s="10" t="n"/>
       <c r="K82" s="11" t="n"/>
       <c r="L82" s="11" t="inlineStr">
         <is>
-          <t>만든 시각</t>
+          <t>초대로 들어온 멤버면 그 초대 (만든 사람은 비움). 초대 행이 지워지면 NULL (fk_mms_project_members_invitation_id)</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4564,7 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
@@ -4563,49 +4588,573 @@
       <c r="K83" s="11" t="n"/>
       <c r="L83" s="11" t="inlineStr">
         <is>
+          <t>만든 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 멤버</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="11" t="n"/>
+      <c r="L84" s="11" t="inlineStr">
+        <is>
           <t>마지막 수정 시각</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="6" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="n"/>
+      <c r="J85" s="10" t="n"/>
+      <c r="K85" s="11" t="n"/>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>초대 번호 (취소 API 경로에 씀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G86" s="11" t="n"/>
+      <c r="H86" s="10" t="n"/>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects.id</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>Y (project_id, email) 살아 있는 초대만</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="n"/>
+      <c r="L86" s="11" t="inlineStr">
+        <is>
+          <t>프로젝트. 프로젝트 행이 지워지면 같이 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="11" t="n"/>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>Y (project_id, email) 살아 있는 초대만</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>ix_mms_project_invitations_email</t>
+        </is>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>초대받은 이메일 (소문자 저장). 로그에 남기지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G88" s="11" t="n"/>
+      <c r="H88" s="10" t="n"/>
+      <c r="I88" s="11" t="n"/>
+      <c r="J88" s="10" t="n"/>
+      <c r="K88" s="11" t="n"/>
+      <c r="L88" s="11" t="inlineStr">
+        <is>
+          <t>수락하면 받을 역할 ADMIN/MEMBER. CHECK (ck_mms_project_invitations_role)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>token_hash</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="11" t="n"/>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="n"/>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>링크 토큰의 HMAC 해시 (core.security.hash_secret). 원문은 메일에만</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>invited_by</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="11" t="n"/>
+      <c r="L90" s="11" t="inlineStr">
+        <is>
+          <t>초대한 프로젝트 관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>expires_at</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="11" t="n"/>
+      <c r="J91" s="10" t="n"/>
+      <c r="K91" s="11" t="n"/>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>만료 시각 (보낸 때 + 7일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>accepted_at</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="n"/>
+      <c r="H92" s="10" t="n"/>
+      <c r="I92" s="11" t="n"/>
+      <c r="J92" s="10" t="n"/>
+      <c r="K92" s="11" t="n"/>
+      <c r="L92" s="11" t="inlineStr">
+        <is>
+          <t>수락 시각. 값이 있으면 다시 못 씀 (1회)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>accepted_user_id</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="J93" s="10" t="n"/>
+      <c r="K93" s="11" t="n"/>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>수락한 회원</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>revoked_at</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G94" s="11" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="11" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="11" t="n"/>
+      <c r="L94" s="11" t="inlineStr">
+        <is>
+          <t>취소 시각 (관리자가 취소하거나 같은 이메일로 다시 초대하면 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>매무새 프로젝트 초대</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="11" t="n"/>
+      <c r="J95" s="10" t="n"/>
+      <c r="K95" s="11" t="n"/>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>보낸 시각 (대기 목록 정렬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>alembic_version</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>마이그레이션 버전</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>version_num</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>VARCHAR(32)</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr"/>
-      <c r="J84" s="6" t="inlineStr"/>
-      <c r="K84" s="8" t="inlineStr"/>
-      <c r="L84" s="8" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr"/>
+      <c r="J96" s="6" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr"/>
+      <c r="L96" s="8" t="inlineStr">
         <is>
           <t>현재 마이그레이션 리비전</t>
         </is>
@@ -4623,7 +5172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4986,9 +5535,136 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>mms_projects.id</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>프로젝트 행이 지워지면 초대도 삭제</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>invited_by</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>제한(NO ACTION)</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>초대한 사람 (회원은 실제로 지우지 않음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>mms_project_invitations</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>accepted_user_id</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>제한(NO ACTION)</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>수락한 회원</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>mms_project_members</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>invitation_id</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>mms_project_invitations.id</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>N:1 (선택)</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>초대로 들어온 멤버. 초대가 지워져도 멤버는 남음</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>참고: 회원은 실제로 지우지 않고(탈퇴는 deactivated_at, 365일 뒤 개인정보만 파기), 행을 남겨 다른 데이터의 참조가 깨지지 않게 합니다.</t>
         </is>

--- a/docs/MeerKit_테이블명세서.xlsx
+++ b/docs/MeerKit_테이블명세서.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>7b35839667fd</t>
+          <t>fe7e50e05dfc</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>feat/maemusae-invites (매무새 초대 추가)</t>
+          <t>feat/maemusae-documents (매무새 문서·올린 파일·쪽 본문 추가)</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-25 (2026-10-27 users.avatar_key 추가, 2026-10-29 common_code_groups·common_codes, mms_projects·mms_project_members, mms_project_invitations·mms_project_members.invitation_id 추가). 소셜 로그인(social_accounts, users.has_password)은 아직 미반영</t>
+          <t>2026-10-25 (2026-10-27 users.avatar_key 추가, 2026-10-29 common_code_groups·common_codes, mms_projects·mms_project_members, mms_project_invitations·mms_project_members.invitation_id, mms_documents·mms_source_files·mms_source_pages 추가). 소셜 로그인(social_accounts, users.has_password)은 아직 미반영</t>
         </is>
       </c>
     </row>
@@ -903,31 +903,100 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>프로젝트의 파일 카드 (요구사항정의서 등, 종류는 공통코드 MMS_DOC_KIND). 프로젝트마다 종류별 하나, 상태는 CHECK</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>문서에 올린 파일 또는 직접 쓴 글. 원본은 비공개 저장소(storage_key), 같은 파일 중복 금지, 문서당 20개</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>mms_source_pages</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>매무새 쪽 본문</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>올린 파일을 MarkItDown 으로 바꾼 마크다운 본문을 쪽(위치) 단위로 저장. PDF 쪽·슬라이드·시트·제목 단위</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
           <t>alembic_version</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>마이그레이션 버전</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Alembic이 관리. 직접 수정하지 않음</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E27" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="D25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="E25" s="9" t="n">
-        <v>95</v>
+      <c r="E28" s="9" t="n">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5117,44 +5186,1352 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="n">
+      <c r="A96" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="n"/>
+      <c r="J96" s="10" t="n"/>
+      <c r="K96" s="11" t="n"/>
+      <c r="L96" s="11" t="inlineStr">
+        <is>
+          <t>문서 번호 (API 경로에 씀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>mms_projects.id</t>
+        </is>
+      </c>
+      <c r="J97" s="10" t="inlineStr">
+        <is>
+          <t>Y (project_id, kind)</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="n"/>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
+          <t>프로젝트. 프로젝트 행이 지워지면 같이 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="n"/>
+      <c r="H98" s="10" t="n"/>
+      <c r="I98" s="11" t="n"/>
+      <c r="J98" s="10" t="inlineStr">
+        <is>
+          <t>Y (project_id, kind)</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="n"/>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>문서 종류. 공통코드 MMS_DOC_KIND (REQUIREMENTS 요구사항정의서 등). 프로젝트를 만들면 REQUIREMENTS 1행</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>'EMPTY'</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="11" t="n"/>
+      <c r="J99" s="10" t="n"/>
+      <c r="K99" s="11" t="n"/>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>EMPTY/ANALYZING/READY/CONFIRMING/CONFIRMED/FAILED. CHECK (ck_mms_documents_status). 분석·확정 중에는 파일 변경 409</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>current_revision</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="11" t="n"/>
+      <c r="J100" s="10" t="n"/>
+      <c r="K100" s="11" t="n"/>
+      <c r="L100" s="11" t="inlineStr">
+        <is>
+          <t>마지막 확정 번호 (M4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>saved_at</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="n"/>
+      <c r="H101" s="10" t="n"/>
+      <c r="I101" s="11" t="n"/>
+      <c r="J101" s="10" t="n"/>
+      <c r="K101" s="11" t="n"/>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>임시 저장 시각 (M3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>saved_by</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G102" s="11" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="11" t="n"/>
+      <c r="L102" s="11" t="inlineStr">
+        <is>
+          <t>임시 저장한 사람</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>confirmed_at</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="n"/>
+      <c r="H103" s="10" t="n"/>
+      <c r="I103" s="11" t="n"/>
+      <c r="J103" s="10" t="n"/>
+      <c r="K103" s="11" t="n"/>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>확정 시각 (M4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>confirmed_by</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G104" s="11" t="n"/>
+      <c r="H104" s="10" t="n"/>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="J104" s="10" t="n"/>
+      <c r="K104" s="11" t="n"/>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>확정한 프로젝트 관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="11" t="n"/>
+      <c r="J105" s="10" t="n"/>
+      <c r="K105" s="11" t="n"/>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>만든 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>매무새 문서</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="11" t="n"/>
+      <c r="J106" s="10" t="n"/>
+      <c r="K106" s="11" t="n"/>
+      <c r="L106" s="11" t="inlineStr">
+        <is>
+          <t>마지막 수정 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="n"/>
+      <c r="J107" s="10" t="n"/>
+      <c r="K107" s="11" t="n"/>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>올린 파일 번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>document_id</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G108" s="11" t="n"/>
+      <c r="H108" s="10" t="n"/>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>mms_documents.id</t>
+        </is>
+      </c>
+      <c r="J108" s="10" t="inlineStr">
+        <is>
+          <t>Y (document_id, sha256) sha256 있을 때만</t>
+        </is>
+      </c>
+      <c r="K108" s="11" t="inlineStr">
+        <is>
+          <t>ix_mms_source_files_document_id</t>
+        </is>
+      </c>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>문서. 문서 행이 지워지면 같이 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="11" t="n"/>
+      <c r="J109" s="10" t="n"/>
+      <c r="K109" s="11" t="n"/>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>FILE 올린 파일 / TEXT 직접 쓴 글. CHECK (ck_mms_source_files_source_type)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>filename</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G110" s="11" t="n"/>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="11" t="n"/>
+      <c r="J110" s="10" t="n"/>
+      <c r="K110" s="11" t="n"/>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>원래 파일 이름 (경로·제어 문자 제거). 로그·저장소 key 에는 넣지 않음. FILE이면 필수 (ck_mms_source_files_file_fields)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="n"/>
+      <c r="H111" s="10" t="n"/>
+      <c r="I111" s="11" t="n"/>
+      <c r="J111" s="10" t="n"/>
+      <c r="K111" s="11" t="n"/>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>확장자로 정한 형식 (브라우저가 보낸 값은 믿지 않음). FILE이면 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>size_bytes</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G112" s="11" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="10" t="n"/>
+      <c r="K112" s="11" t="n"/>
+      <c r="L112" s="11" t="inlineStr">
+        <is>
+          <t>파일 크기 (10MB 한도, MMS_SOURCE_MAX_BYTES). FILE이면 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="n"/>
+      <c r="H113" s="10" t="n"/>
+      <c r="I113" s="11" t="n"/>
+      <c r="J113" s="10" t="inlineStr">
+        <is>
+          <t>Y (document_id, sha256) sha256 있을 때만</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="n"/>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>같은 파일 중복 확인 (409 SOURCE_DUPLICATE). FILE이면 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>storage_key</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(300)</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G114" s="11" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="11" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="11" t="n"/>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>원본의 비공개 저장소 key (mms/projects/{id}/sources/{무작위}). 공개 버킷에는 넣지 않음. FILE이면 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>page_count</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="11" t="n"/>
+      <c r="J115" s="10" t="n"/>
+      <c r="K115" s="11" t="n"/>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>나눈 쪽(위치) 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>parse_status</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>'PARSED'</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="n"/>
+      <c r="I116" s="11" t="n"/>
+      <c r="J116" s="10" t="n"/>
+      <c r="K116" s="11" t="n"/>
+      <c r="L116" s="11" t="inlineStr">
+        <is>
+          <t>PARSED/FAILED. CHECK. 지금은 변환에 실패한 파일은 저장하지 않으므로 PARSED만</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>uploaded_by</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="J117" s="10" t="n"/>
+      <c r="K117" s="11" t="n"/>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>올린 사람 (지우기는 올린 사람 또는 프로젝트 관리자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>매무새 올린 파일</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="n"/>
+      <c r="I118" s="11" t="n"/>
+      <c r="J118" s="10" t="n"/>
+      <c r="K118" s="11" t="n"/>
+      <c r="L118" s="11" t="inlineStr">
+        <is>
+          <t>올린 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_pages</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>매무새 쪽 본문</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>자동 증가</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="n"/>
+      <c r="J119" s="10" t="n"/>
+      <c r="K119" s="11" t="n"/>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>쪽 번호 (내부 PK, 근거가 가리킴 M3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_pages</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>매무새 쪽 본문</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>source_file_id</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="n"/>
+      <c r="H120" s="10" t="n"/>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_files.id</t>
+        </is>
+      </c>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>Y (source_file_id, seq)</t>
+        </is>
+      </c>
+      <c r="K120" s="11" t="n"/>
+      <c r="L120" s="11" t="inlineStr">
+        <is>
+          <t>올린 파일. 파일 행이 지워지면 같이 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_pages</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>매무새 쪽 본문</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>seq</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="n"/>
+      <c r="H121" s="10" t="n"/>
+      <c r="I121" s="11" t="n"/>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>Y (source_file_id, seq)</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="n"/>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>파일 안 순서 (1부터). 다음 쪽은 seq + 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_pages</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>매무새 쪽 본문</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>page_no</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G122" s="11" t="n"/>
+      <c r="H122" s="10" t="n"/>
+      <c r="I122" s="11" t="n"/>
+      <c r="J122" s="10" t="n"/>
+      <c r="K122" s="11" t="n"/>
+      <c r="L122" s="11" t="inlineStr">
+        <is>
+          <t>진짜 쪽 번호가 있을 때만 (PDF 쪽, PPT 슬라이드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_pages</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>매무새 쪽 본문</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>location_label</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="n"/>
+      <c r="H123" s="10" t="n"/>
+      <c r="I123" s="11" t="n"/>
+      <c r="J123" s="10" t="n"/>
+      <c r="K123" s="11" t="n"/>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>화면 위치 표시: 3쪽, 슬라이드 4, 시트 '요구사항', 2. 결제 요구사항, 1부분, 직접 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_pages</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>매무새 쪽 본문</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G124" s="11" t="n"/>
+      <c r="H124" s="10" t="n"/>
+      <c r="I124" s="11" t="n"/>
+      <c r="J124" s="10" t="n"/>
+      <c r="K124" s="11" t="n"/>
+      <c r="L124" s="11" t="inlineStr">
+        <is>
+          <t>그 위치의 마크다운 본문 (MarkItDown 변환). 고객 문서라 로그 금지, 멤버만 봄</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>mms_source_pages</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>매무새 쪽 본문</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="n"/>
+      <c r="I125" s="11" t="n"/>
+      <c r="J125" s="10" t="n"/>
+      <c r="K125" s="11" t="n"/>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>만든 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>alembic_version</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C126" s="8" t="inlineStr">
         <is>
           <t>마이그레이션 버전</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="D126" s="8" t="inlineStr">
         <is>
           <t>version_num</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="E126" s="8" t="inlineStr">
         <is>
           <t>VARCHAR(32)</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr"/>
+      <c r="H126" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="I96" s="8" t="inlineStr"/>
-      <c r="J96" s="6" t="inlineStr"/>
-      <c r="K96" s="8" t="inlineStr"/>
-      <c r="L96" s="8" t="inlineStr">
+      <c r="I126" s="8" t="inlineStr"/>
+      <c r="J126" s="6" t="inlineStr"/>
+      <c r="K126" s="8" t="inlineStr"/>
+      <c r="L126" s="8" t="inlineStr">
         <is>
           <t>현재 마이그레이션 리비전</t>
         </is>
@@ -5172,7 +6549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5663,8 +7040,169 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>mms_projects.id</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>프로젝트 행이 지워지면 문서도 삭제 (보관 기간 뒤 정리 명령)</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>mms_documents</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>saved_by / confirmed_by</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>N:1 (선택)</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>제한(NO ACTION)</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>임시 저장·확정한 사람</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>document_id</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>mms_documents.id</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>문서가 지워지면 올린 파일 행도 삭제 (원본은 서비스·정리 명령이 저장소에서 지움)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>mms_source_files</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>uploaded_by</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>users.id</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>제한(NO ACTION)</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>올린 사람</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>mms_source_pages</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>source_file_id</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>mms_source_files.id</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>N:1</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>올린 파일을 지우면 쪽 본문도 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>참고: 회원은 실제로 지우지 않고(탈퇴는 deactivated_at, 365일 뒤 개인정보만 파기), 행을 남겨 다른 데이터의 참조가 깨지지 않게 합니다.</t>
         </is>
